--- a/artfynd/A 52386-2025 artfynd.xlsx
+++ b/artfynd/A 52386-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129644777</v>
       </c>
       <c r="B3" t="n">
-        <v>96352</v>
+        <v>96364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129644779</v>
       </c>
       <c r="B4" t="n">
-        <v>105822</v>
+        <v>105834</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>129644776</v>
       </c>
       <c r="B5" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52386-2025 artfynd.xlsx
+++ b/artfynd/A 52386-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129644777</v>
       </c>
       <c r="B3" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129644779</v>
       </c>
       <c r="B4" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>129644776</v>
       </c>
       <c r="B5" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52386-2025 artfynd.xlsx
+++ b/artfynd/A 52386-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129644777</v>
       </c>
       <c r="B3" t="n">
-        <v>96365</v>
+        <v>96370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129644779</v>
       </c>
       <c r="B4" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>129644776</v>
       </c>
       <c r="B5" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52386-2025 artfynd.xlsx
+++ b/artfynd/A 52386-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129644777</v>
       </c>
       <c r="B3" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129644779</v>
       </c>
       <c r="B4" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>129644776</v>
       </c>
       <c r="B5" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52386-2025 artfynd.xlsx
+++ b/artfynd/A 52386-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129644777</v>
       </c>
       <c r="B3" t="n">
-        <v>96374</v>
+        <v>96376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129644779</v>
       </c>
       <c r="B4" t="n">
-        <v>105844</v>
+        <v>105846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>129644776</v>
       </c>
       <c r="B5" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52386-2025 artfynd.xlsx
+++ b/artfynd/A 52386-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129644777</v>
       </c>
       <c r="B3" t="n">
-        <v>96376</v>
+        <v>96386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129644779</v>
       </c>
       <c r="B4" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52386-2025 artfynd.xlsx
+++ b/artfynd/A 52386-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129644777</v>
       </c>
       <c r="B3" t="n">
-        <v>96386</v>
+        <v>96390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129644779</v>
       </c>
       <c r="B4" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>129644776</v>
       </c>
       <c r="B5" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52386-2025 artfynd.xlsx
+++ b/artfynd/A 52386-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129644777</v>
       </c>
       <c r="B3" t="n">
-        <v>96390</v>
+        <v>96393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129644779</v>
       </c>
       <c r="B4" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>129644776</v>
       </c>
       <c r="B5" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52386-2025 artfynd.xlsx
+++ b/artfynd/A 52386-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129644777</v>
       </c>
       <c r="B3" t="n">
-        <v>96393</v>
+        <v>96394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129644779</v>
       </c>
       <c r="B4" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>129644776</v>
       </c>
       <c r="B5" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52386-2025 artfynd.xlsx
+++ b/artfynd/A 52386-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64645060</v>
+        <v>129644777</v>
       </c>
       <c r="B2" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ostlänken Nyköpings kommun, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580440.0688037031</v>
+        <v>580195</v>
       </c>
       <c r="R2" t="n">
-        <v>6511050.176628137</v>
+        <v>6511039</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-10-10</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>CallunaAB</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,26 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tenna Toftegaard</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Ostlänken Nyköpings kommun (Calluna_HIL0097B)</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Birgitta Hamstedt</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129644777</v>
+        <v>64645060</v>
       </c>
       <c r="B3" t="n">
-        <v>96394</v>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,41 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Ostlänken Nyköpings kommun, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580195</v>
+        <v>580440</v>
       </c>
       <c r="R3" t="n">
-        <v>6511039</v>
+        <v>6511050</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2015-10-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2015-10-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>CallunaAB</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,50 +876,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Tenna Toftegaard</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Birgitta Hamstedt</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ostlänken Nyköpings kommun (Calluna_HIL0097B)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129644779</v>
+        <v>129644776</v>
       </c>
       <c r="B4" t="n">
-        <v>105864</v>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580444</v>
+        <v>580191</v>
       </c>
       <c r="R4" t="n">
-        <v>6510951</v>
+        <v>6510984</v>
       </c>
       <c r="S4" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,14 +979,14 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1018,41 +1006,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129644776</v>
+        <v>129644779</v>
       </c>
       <c r="B5" t="n">
-        <v>92926</v>
+        <v>106243</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,13 +1045,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580191</v>
+        <v>580444</v>
       </c>
       <c r="R5" t="n">
-        <v>6510984</v>
+        <v>6510951</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,14 +1090,14 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>

--- a/artfynd/A 52386-2025 artfynd.xlsx
+++ b/artfynd/A 52386-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129644777</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
           <t>Ostlänken Nyköpings kommun (Calluna_HIL0097B)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64645060</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129644776</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,8 +1134,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129644779</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>